--- a/doc/FPGA_MSXtR_Stack_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_Stack_TangFPGA_pin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134B2502-27EC-48A5-93A6-8BC9D88EAB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA6E0B5-E928-455D-A937-CD0462AD9BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="342">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1370,6 +1370,10 @@
   </si>
   <si>
     <t>slot_oe_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_data_dir</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1693,7 +1697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1809,28 +1813,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1865,8 +1854,11 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2721,40 +2713,40 @@
     </row>
     <row r="2" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:28" x14ac:dyDescent="0.15">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="47" t="s">
         <v>2</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -2871,8 +2863,12 @@
         <v>5</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="9"/>
+      <c r="F5" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="I5" s="5">
         <v>4</v>
       </c>
@@ -2889,7 +2885,7 @@
       <c r="N5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="53">
+      <c r="P5" s="48">
         <v>63</v>
       </c>
       <c r="Q5" s="1" t="s">
@@ -2899,13 +2895,13 @@
         <v>0</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="54" t="s">
+      <c r="T5" s="49" t="s">
         <v>150</v>
       </c>
       <c r="U5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="53">
+      <c r="W5" s="48">
         <v>64</v>
       </c>
       <c r="X5" s="1" t="s">
@@ -2917,7 +2913,7 @@
       <c r="Z5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA5" s="55" t="s">
+      <c r="AA5" s="50" t="s">
         <v>152</v>
       </c>
       <c r="AB5" s="9" t="s">
@@ -2935,8 +2931,12 @@
         <v>5</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="49" t="s">
+        <v>340</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="I6" s="8">
         <v>6</v>
       </c>
@@ -2947,13 +2947,13 @@
         <v>2</v>
       </c>
       <c r="L6" s="1"/>
-      <c r="M6" s="54" t="s">
-        <v>156</v>
+      <c r="M6" s="49" t="s">
+        <v>341</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="48">
         <v>65</v>
       </c>
       <c r="Q6" s="1" t="s">
@@ -2963,13 +2963,13 @@
         <v>0</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="54" t="s">
+      <c r="T6" s="49" t="s">
         <v>158</v>
       </c>
       <c r="U6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W6" s="53">
+      <c r="W6" s="48">
         <v>66</v>
       </c>
       <c r="X6" s="1" t="s">
@@ -2981,7 +2981,7 @@
       <c r="Z6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA6" s="54" t="s">
+      <c r="AA6" s="49" t="s">
         <v>319</v>
       </c>
       <c r="AB6" s="9" t="s">
@@ -3017,13 +3017,9 @@
         <v>2</v>
       </c>
       <c r="L7" s="1"/>
-      <c r="M7" s="54" t="s">
-        <v>340</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="P7" s="53">
+      <c r="M7" s="1"/>
+      <c r="N7" s="9"/>
+      <c r="P7" s="48">
         <v>67</v>
       </c>
       <c r="Q7" s="1" t="s">
@@ -3035,13 +3031,13 @@
       <c r="S7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T7" s="54" t="s">
+      <c r="T7" s="49" t="s">
         <v>166</v>
       </c>
       <c r="U7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W7" s="53">
+      <c r="W7" s="48">
         <v>68</v>
       </c>
       <c r="X7" s="1" t="s">
@@ -3053,7 +3049,7 @@
       <c r="Z7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA7" s="54" t="s">
+      <c r="AA7" s="49" t="s">
         <v>168</v>
       </c>
       <c r="AB7" s="9" t="s">
@@ -3091,7 +3087,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="9"/>
-      <c r="P8" s="53">
+      <c r="P8" s="48">
         <v>69</v>
       </c>
       <c r="Q8" s="1" t="s">
@@ -3103,13 +3099,13 @@
       <c r="S8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T8" s="54" t="s">
+      <c r="T8" s="49" t="s">
         <v>173</v>
       </c>
       <c r="U8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W8" s="53">
+      <c r="W8" s="48">
         <v>70</v>
       </c>
       <c r="X8" s="1" t="s">
@@ -3121,7 +3117,7 @@
       <c r="Z8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA8" s="54" t="s">
+      <c r="AA8" s="49" t="s">
         <v>175</v>
       </c>
       <c r="AB8" s="9" t="s">
@@ -3157,7 +3153,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="9"/>
-      <c r="P9" s="53">
+      <c r="P9" s="48">
         <v>71</v>
       </c>
       <c r="Q9" s="1" t="s">
@@ -3169,13 +3165,13 @@
       <c r="S9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T9" s="54" t="s">
+      <c r="T9" s="49" t="s">
         <v>180</v>
       </c>
       <c r="U9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W9" s="53">
+      <c r="W9" s="48">
         <v>72</v>
       </c>
       <c r="X9" s="1" t="s">
@@ -3185,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="54" t="s">
+      <c r="AA9" s="49" t="s">
         <v>182</v>
       </c>
       <c r="AB9" s="9" t="s">
@@ -3223,7 +3219,7 @@
       <c r="N10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="53">
+      <c r="P10" s="48">
         <v>73</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -3235,13 +3231,13 @@
       <c r="S10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T10" s="54" t="s">
+      <c r="T10" s="49" t="s">
         <v>187</v>
       </c>
       <c r="U10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W10" s="53">
+      <c r="W10" s="48">
         <v>74</v>
       </c>
       <c r="X10" s="1" t="s">
@@ -3251,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="54" t="s">
+      <c r="AA10" s="49" t="s">
         <v>189</v>
       </c>
       <c r="AB10" s="9" t="s">
@@ -3309,7 +3305,7 @@
       <c r="U11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W11" s="53">
+      <c r="W11" s="48">
         <v>76</v>
       </c>
       <c r="X11" s="1" t="s">
@@ -3319,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="54" t="s">
+      <c r="AA11" s="49" t="s">
         <v>194</v>
       </c>
       <c r="AB11" s="9" t="s">
@@ -3361,7 +3357,7 @@
       <c r="N12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P12" s="53">
+      <c r="P12" s="48">
         <v>77</v>
       </c>
       <c r="Q12" s="1" t="s">
@@ -3373,9 +3369,9 @@
       <c r="S12" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T12" s="57"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="9"/>
-      <c r="W12" s="53">
+      <c r="W12" s="48">
         <v>78</v>
       </c>
       <c r="X12" s="1" t="s">
@@ -3385,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="54" t="s">
+      <c r="AA12" s="49" t="s">
         <v>204</v>
       </c>
       <c r="AB12" s="9" t="s">
@@ -3443,7 +3439,7 @@
       <c r="U13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="W13" s="53">
+      <c r="W13" s="48">
         <v>80</v>
       </c>
       <c r="X13" s="1" t="s">
@@ -3453,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="54" t="s">
+      <c r="AA13" s="49" t="s">
         <v>211</v>
       </c>
       <c r="AB13" s="9" t="s">
@@ -3515,7 +3511,7 @@
       <c r="U14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="W14" s="53">
+      <c r="W14" s="48">
         <v>82</v>
       </c>
       <c r="X14" s="1" t="s">
@@ -3525,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="54" t="s">
+      <c r="AA14" s="49" t="s">
         <v>220</v>
       </c>
       <c r="AB14" s="9" t="s">
@@ -3569,7 +3565,7 @@
       <c r="N15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P15" s="53">
+      <c r="P15" s="48">
         <v>83</v>
       </c>
       <c r="Q15" s="1" t="s">
@@ -3641,7 +3637,7 @@
       <c r="N16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P16" s="53">
+      <c r="P16" s="48">
         <v>85</v>
       </c>
       <c r="Q16" s="1" t="s">
@@ -3773,7 +3769,7 @@
       <c r="L18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M18" s="56" t="s">
+      <c r="M18" s="51" t="s">
         <v>320</v>
       </c>
       <c r="N18" s="9" t="s">
@@ -3797,7 +3793,7 @@
       <c r="U18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="53">
+      <c r="W18" s="48">
         <v>90</v>
       </c>
       <c r="X18" s="1" t="s">
@@ -3807,7 +3803,7 @@
         <v>7</v>
       </c>
       <c r="Z18" s="1"/>
-      <c r="AA18" s="54" t="s">
+      <c r="AA18" s="49" t="s">
         <v>242</v>
       </c>
       <c r="AB18" s="9" t="s">
@@ -3839,7 +3835,7 @@
       <c r="L19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M19" s="56" t="s">
+      <c r="M19" s="51" t="s">
         <v>321</v>
       </c>
       <c r="N19" s="9" t="s">
@@ -3863,7 +3859,7 @@
       <c r="U19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W19" s="53">
+      <c r="W19" s="48">
         <v>92</v>
       </c>
       <c r="X19" s="1" t="s">
@@ -3873,7 +3869,7 @@
         <v>7</v>
       </c>
       <c r="Z19" s="1"/>
-      <c r="AA19" s="54" t="s">
+      <c r="AA19" s="49" t="s">
         <v>249</v>
       </c>
       <c r="AB19" s="9" t="s">
@@ -3905,13 +3901,13 @@
       <c r="L20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="56" t="s">
+      <c r="M20" s="51" t="s">
         <v>322</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P20" s="53">
+      <c r="P20" s="48">
         <v>93</v>
       </c>
       <c r="Q20" s="1" t="s">
@@ -3923,13 +3919,13 @@
       <c r="S20" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T20" s="54" t="s">
+      <c r="T20" s="49" t="s">
         <v>254</v>
       </c>
       <c r="U20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W20" s="53">
+      <c r="W20" s="48">
         <v>94</v>
       </c>
       <c r="X20" s="1" t="s">
@@ -3939,7 +3935,7 @@
         <v>7</v>
       </c>
       <c r="Z20" s="1"/>
-      <c r="AA20" s="54" t="s">
+      <c r="AA20" s="49" t="s">
         <v>256</v>
       </c>
       <c r="AB20" s="9" t="s">
@@ -3975,13 +3971,13 @@
       <c r="L21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="56" t="s">
+      <c r="M21" s="51" t="s">
         <v>323</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P21" s="53">
+      <c r="P21" s="48">
         <v>95</v>
       </c>
       <c r="Q21" s="1" t="s">
@@ -3993,13 +3989,13 @@
       <c r="S21" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T21" s="54" t="s">
+      <c r="T21" s="49" t="s">
         <v>260</v>
       </c>
       <c r="U21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W21" s="53">
+      <c r="W21" s="48">
         <v>96</v>
       </c>
       <c r="X21" s="1" t="s">
@@ -4009,7 +4005,7 @@
         <v>7</v>
       </c>
       <c r="Z21" s="1"/>
-      <c r="AA21" s="54" t="s">
+      <c r="AA21" s="49" t="s">
         <v>262</v>
       </c>
       <c r="AB21" s="9" t="s">
@@ -4043,7 +4039,7 @@
       </c>
       <c r="M22" s="6"/>
       <c r="N22" s="7"/>
-      <c r="P22" s="53">
+      <c r="P22" s="48">
         <v>97</v>
       </c>
       <c r="Q22" s="1" t="s">
@@ -4055,13 +4051,13 @@
       <c r="S22" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T22" s="54" t="s">
+      <c r="T22" s="49" t="s">
         <v>333</v>
       </c>
       <c r="U22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W22" s="53">
+      <c r="W22" s="48">
         <v>98</v>
       </c>
       <c r="X22" s="1" t="s">
@@ -4071,7 +4067,7 @@
         <v>7</v>
       </c>
       <c r="Z22" s="1"/>
-      <c r="AA22" s="54" t="s">
+      <c r="AA22" s="49" t="s">
         <v>268</v>
       </c>
       <c r="AB22" s="9" t="s">
@@ -4105,7 +4101,7 @@
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="7"/>
-      <c r="P23" s="53">
+      <c r="P23" s="48">
         <v>99</v>
       </c>
       <c r="Q23" s="1" t="s">
@@ -4117,13 +4113,13 @@
       <c r="S23" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T23" s="54" t="s">
+      <c r="T23" s="49" t="s">
         <v>334</v>
       </c>
       <c r="U23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W23" s="53">
+      <c r="W23" s="48">
         <v>100</v>
       </c>
       <c r="X23" s="1" t="s">
@@ -4133,7 +4129,7 @@
         <v>7</v>
       </c>
       <c r="Z23" s="1"/>
-      <c r="AA23" s="54" t="s">
+      <c r="AA23" s="49" t="s">
         <v>273</v>
       </c>
       <c r="AB23" s="9" t="s">
@@ -4171,7 +4167,7 @@
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="7"/>
-      <c r="P24" s="53">
+      <c r="P24" s="48">
         <v>101</v>
       </c>
       <c r="Q24" s="1" t="s">
@@ -4181,13 +4177,13 @@
         <v>7</v>
       </c>
       <c r="S24" s="1"/>
-      <c r="T24" s="54" t="s">
+      <c r="T24" s="49" t="s">
         <v>335</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W24" s="53">
+      <c r="W24" s="48">
         <v>102</v>
       </c>
       <c r="X24" s="1" t="s">
@@ -4197,7 +4193,7 @@
         <v>7</v>
       </c>
       <c r="Z24" s="1"/>
-      <c r="AA24" s="54" t="s">
+      <c r="AA24" s="49" t="s">
         <v>278</v>
       </c>
       <c r="AB24" s="9" t="s">
@@ -4231,7 +4227,7 @@
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="7"/>
-      <c r="P25" s="53">
+      <c r="P25" s="48">
         <v>103</v>
       </c>
       <c r="Q25" s="1" t="s">
@@ -4241,13 +4237,13 @@
         <v>7</v>
       </c>
       <c r="S25" s="1"/>
-      <c r="T25" s="54" t="s">
+      <c r="T25" s="49" t="s">
         <v>281</v>
       </c>
       <c r="U25" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W25" s="53">
+      <c r="W25" s="48">
         <v>104</v>
       </c>
       <c r="X25" s="1" t="s">
@@ -4257,7 +4253,7 @@
         <v>7</v>
       </c>
       <c r="Z25" s="1"/>
-      <c r="AA25" s="54" t="s">
+      <c r="AA25" s="49" t="s">
         <v>283</v>
       </c>
       <c r="AB25" s="9" t="s">
@@ -4307,7 +4303,7 @@
       <c r="U26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W26" s="53">
+      <c r="W26" s="48">
         <v>106</v>
       </c>
       <c r="X26" s="1" t="s">
@@ -4317,7 +4313,7 @@
         <v>7</v>
       </c>
       <c r="Z26" s="1"/>
-      <c r="AA26" s="54" t="s">
+      <c r="AA26" s="49" t="s">
         <v>287</v>
       </c>
       <c r="AB26" s="9" t="s">
@@ -4355,7 +4351,7 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="7"/>
-      <c r="P27" s="53">
+      <c r="P27" s="48">
         <v>107</v>
       </c>
       <c r="Q27" s="1" t="s">
@@ -4365,13 +4361,13 @@
         <v>6</v>
       </c>
       <c r="S27" s="1"/>
-      <c r="T27" s="54" t="s">
+      <c r="T27" s="49" t="s">
         <v>289</v>
       </c>
       <c r="U27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W27" s="53">
+      <c r="W27" s="48">
         <v>108</v>
       </c>
       <c r="X27" s="1" t="s">
@@ -4381,7 +4377,7 @@
         <v>7</v>
       </c>
       <c r="Z27" s="1"/>
-      <c r="AA27" s="54" t="s">
+      <c r="AA27" s="49" t="s">
         <v>291</v>
       </c>
       <c r="AB27" s="9" t="s">
@@ -4415,7 +4411,7 @@
       </c>
       <c r="M28" s="6"/>
       <c r="N28" s="7"/>
-      <c r="P28" s="53">
+      <c r="P28" s="48">
         <v>109</v>
       </c>
       <c r="Q28" s="1" t="s">
@@ -4425,7 +4421,7 @@
         <v>6</v>
       </c>
       <c r="S28" s="1"/>
-      <c r="T28" s="54" t="s">
+      <c r="T28" s="49" t="s">
         <v>294</v>
       </c>
       <c r="U28" s="9" t="s">
@@ -4475,7 +4471,7 @@
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="7"/>
-      <c r="P29" s="53">
+      <c r="P29" s="48">
         <v>111</v>
       </c>
       <c r="Q29" s="1" t="s">
@@ -4487,13 +4483,13 @@
       <c r="S29" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T29" s="54" t="s">
+      <c r="T29" s="49" t="s">
         <v>336</v>
       </c>
       <c r="U29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W29" s="53">
+      <c r="W29" s="48">
         <v>112</v>
       </c>
       <c r="X29" s="1" t="s">
@@ -4505,7 +4501,7 @@
       <c r="Z29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="54" t="s">
+      <c r="AA29" s="49" t="s">
         <v>202</v>
       </c>
       <c r="AB29" s="9" t="s">
@@ -4543,7 +4539,7 @@
       </c>
       <c r="M30" s="6"/>
       <c r="N30" s="7"/>
-      <c r="P30" s="53">
+      <c r="P30" s="48">
         <v>113</v>
       </c>
       <c r="Q30" s="1" t="s">
@@ -4555,13 +4551,13 @@
       <c r="S30" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T30" s="54" t="s">
+      <c r="T30" s="49" t="s">
         <v>337</v>
       </c>
       <c r="U30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W30" s="53">
+      <c r="W30" s="48">
         <v>114</v>
       </c>
       <c r="X30" s="1" t="s">
@@ -4573,7 +4569,7 @@
       <c r="Z30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA30" s="54" t="s">
+      <c r="AA30" s="49" t="s">
         <v>226</v>
       </c>
       <c r="AB30" s="9" t="s">
@@ -4607,7 +4603,7 @@
       </c>
       <c r="M31" s="6"/>
       <c r="N31" s="7"/>
-      <c r="P31" s="53">
+      <c r="P31" s="48">
         <v>115</v>
       </c>
       <c r="Q31" s="1" t="s">
@@ -4619,13 +4615,13 @@
       <c r="S31" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="T31" s="54" t="s">
+      <c r="T31" s="49" t="s">
         <v>338</v>
       </c>
       <c r="U31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W31" s="53">
+      <c r="W31" s="48">
         <v>116</v>
       </c>
       <c r="X31" s="1" t="s">
@@ -4635,7 +4631,7 @@
         <v>6</v>
       </c>
       <c r="Z31" s="1"/>
-      <c r="AA31" s="54" t="s">
+      <c r="AA31" s="49" t="s">
         <v>317</v>
       </c>
       <c r="AB31" s="9" t="s">
@@ -4669,7 +4665,7 @@
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="7"/>
-      <c r="P32" s="53">
+      <c r="P32" s="48">
         <v>117</v>
       </c>
       <c r="Q32" s="1" t="s">
@@ -4679,13 +4675,13 @@
         <v>6</v>
       </c>
       <c r="S32" s="1"/>
-      <c r="T32" s="54" t="s">
+      <c r="T32" s="49" t="s">
         <v>339</v>
       </c>
       <c r="U32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W32" s="53">
+      <c r="W32" s="48">
         <v>118</v>
       </c>
       <c r="X32" s="1" t="s">
@@ -4695,7 +4691,7 @@
         <v>6</v>
       </c>
       <c r="Z32" s="1"/>
-      <c r="AA32" s="54" t="s">
+      <c r="AA32" s="49" t="s">
         <v>318</v>
       </c>
       <c r="AB32" s="9" t="s">
@@ -4803,40 +4799,40 @@
     </row>
     <row r="2" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:28" x14ac:dyDescent="0.15">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="47" t="s">
         <v>2</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -4971,7 +4967,7 @@
       <c r="N5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="53">
+      <c r="P5" s="48">
         <v>63</v>
       </c>
       <c r="Q5" s="1" t="s">
@@ -4981,13 +4977,13 @@
         <v>0</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="54" t="s">
+      <c r="T5" s="49" t="s">
         <v>150</v>
       </c>
       <c r="U5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W5" s="53">
+      <c r="W5" s="48">
         <v>64</v>
       </c>
       <c r="X5" s="1" t="s">
@@ -4999,7 +4995,7 @@
       <c r="Z5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA5" s="55" t="s">
+      <c r="AA5" s="50" t="s">
         <v>152</v>
       </c>
       <c r="AB5" s="9" t="s">
@@ -5033,13 +5029,13 @@
         <v>2</v>
       </c>
       <c r="L6" s="1"/>
-      <c r="M6" s="54" t="s">
+      <c r="M6" s="49" t="s">
         <v>156</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="48">
         <v>65</v>
       </c>
       <c r="Q6" s="1" t="s">
@@ -5049,13 +5045,13 @@
         <v>0</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="54" t="s">
+      <c r="T6" s="49" t="s">
         <v>158</v>
       </c>
       <c r="U6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="53">
+      <c r="W6" s="48">
         <v>66</v>
       </c>
       <c r="X6" s="1" t="s">
@@ -5067,7 +5063,7 @@
       <c r="Z6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA6" s="54" t="s">
+      <c r="AA6" s="49" t="s">
         <v>160</v>
       </c>
       <c r="AB6" s="9" t="s">
@@ -5105,7 +5101,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="9"/>
-      <c r="P7" s="53">
+      <c r="P7" s="48">
         <v>67</v>
       </c>
       <c r="Q7" s="1" t="s">
@@ -5117,13 +5113,13 @@
       <c r="S7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T7" s="54" t="s">
+      <c r="T7" s="49" t="s">
         <v>166</v>
       </c>
       <c r="U7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="53">
+      <c r="W7" s="48">
         <v>68</v>
       </c>
       <c r="X7" s="1" t="s">
@@ -5135,7 +5131,7 @@
       <c r="Z7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA7" s="54" t="s">
+      <c r="AA7" s="49" t="s">
         <v>168</v>
       </c>
       <c r="AB7" s="9" t="s">
@@ -5173,7 +5169,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="9"/>
-      <c r="P8" s="53">
+      <c r="P8" s="48">
         <v>69</v>
       </c>
       <c r="Q8" s="1" t="s">
@@ -5185,13 +5181,13 @@
       <c r="S8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T8" s="54" t="s">
+      <c r="T8" s="49" t="s">
         <v>173</v>
       </c>
       <c r="U8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W8" s="53">
+      <c r="W8" s="48">
         <v>70</v>
       </c>
       <c r="X8" s="1" t="s">
@@ -5203,7 +5199,7 @@
       <c r="Z8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA8" s="54" t="s">
+      <c r="AA8" s="49" t="s">
         <v>175</v>
       </c>
       <c r="AB8" s="9" t="s">
@@ -5239,7 +5235,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="9"/>
-      <c r="P9" s="53">
+      <c r="P9" s="48">
         <v>71</v>
       </c>
       <c r="Q9" s="1" t="s">
@@ -5251,13 +5247,13 @@
       <c r="S9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T9" s="54" t="s">
+      <c r="T9" s="49" t="s">
         <v>180</v>
       </c>
       <c r="U9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W9" s="53">
+      <c r="W9" s="48">
         <v>72</v>
       </c>
       <c r="X9" s="1" t="s">
@@ -5267,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="54" t="s">
+      <c r="AA9" s="49" t="s">
         <v>182</v>
       </c>
       <c r="AB9" s="9" t="s">
@@ -5301,7 +5297,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="9"/>
-      <c r="P10" s="53">
+      <c r="P10" s="48">
         <v>73</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -5313,13 +5309,13 @@
       <c r="S10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T10" s="54" t="s">
+      <c r="T10" s="49" t="s">
         <v>187</v>
       </c>
       <c r="U10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="53">
+      <c r="W10" s="48">
         <v>74</v>
       </c>
       <c r="X10" s="1" t="s">
@@ -5329,7 +5325,7 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="54" t="s">
+      <c r="AA10" s="49" t="s">
         <v>189</v>
       </c>
       <c r="AB10" s="9" t="s">
@@ -5383,7 +5379,7 @@
       <c r="U11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W11" s="53">
+      <c r="W11" s="48">
         <v>76</v>
       </c>
       <c r="X11" s="1" t="s">
@@ -5393,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="54" t="s">
+      <c r="AA11" s="49" t="s">
         <v>194</v>
       </c>
       <c r="AB11" s="9" t="s">
@@ -5429,13 +5425,13 @@
       <c r="L12" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="M12" s="56" t="s">
+      <c r="M12" s="51" t="s">
         <v>199</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P12" s="53">
+      <c r="P12" s="48">
         <v>77</v>
       </c>
       <c r="Q12" s="1" t="s">
@@ -5447,13 +5443,13 @@
       <c r="S12" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T12" s="55" t="s">
+      <c r="T12" s="50" t="s">
         <v>202</v>
       </c>
       <c r="U12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W12" s="53">
+      <c r="W12" s="48">
         <v>78</v>
       </c>
       <c r="X12" s="1" t="s">
@@ -5463,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="54" t="s">
+      <c r="AA12" s="49" t="s">
         <v>204</v>
       </c>
       <c r="AB12" s="9" t="s">
@@ -5497,7 +5493,7 @@
         <v>2</v>
       </c>
       <c r="L13" s="1"/>
-      <c r="M13" s="56" t="s">
+      <c r="M13" s="51" t="s">
         <v>206</v>
       </c>
       <c r="N13" s="9" t="s">
@@ -5521,7 +5517,7 @@
       <c r="U13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="W13" s="53">
+      <c r="W13" s="48">
         <v>80</v>
       </c>
       <c r="X13" s="1" t="s">
@@ -5531,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="54" t="s">
+      <c r="AA13" s="49" t="s">
         <v>211</v>
       </c>
       <c r="AB13" s="9" t="s">
@@ -5569,7 +5565,7 @@
       <c r="L14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="56" t="s">
+      <c r="M14" s="51" t="s">
         <v>215</v>
       </c>
       <c r="N14" s="9" t="s">
@@ -5593,7 +5589,7 @@
       <c r="U14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="W14" s="53">
+      <c r="W14" s="48">
         <v>82</v>
       </c>
       <c r="X14" s="1" t="s">
@@ -5603,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="54" t="s">
+      <c r="AA14" s="49" t="s">
         <v>220</v>
       </c>
       <c r="AB14" s="9" t="s">
@@ -5641,13 +5637,13 @@
       <c r="L15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="56" t="s">
+      <c r="M15" s="51" t="s">
         <v>224</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P15" s="53">
+      <c r="P15" s="48">
         <v>83</v>
       </c>
       <c r="Q15" s="1" t="s">
@@ -5657,7 +5653,7 @@
         <v>4</v>
       </c>
       <c r="S15" s="1"/>
-      <c r="T15" s="55" t="s">
+      <c r="T15" s="50" t="s">
         <v>226</v>
       </c>
       <c r="U15" s="9" t="s">
@@ -5713,13 +5709,13 @@
       <c r="L16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M16" s="56" t="s">
+      <c r="M16" s="51" t="s">
         <v>231</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P16" s="53">
+      <c r="P16" s="48">
         <v>85</v>
       </c>
       <c r="Q16" s="1" t="s">
@@ -5783,7 +5779,7 @@
       <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="56" t="s">
+      <c r="M17" s="51" t="s">
         <v>237</v>
       </c>
       <c r="N17" s="9" t="s">
@@ -5851,7 +5847,7 @@
       <c r="L18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M18" s="56" t="s">
+      <c r="M18" s="51" t="s">
         <v>239</v>
       </c>
       <c r="N18" s="9" t="s">
@@ -5875,7 +5871,7 @@
       <c r="U18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="53">
+      <c r="W18" s="48">
         <v>90</v>
       </c>
       <c r="X18" s="1" t="s">
@@ -5885,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="Z18" s="1"/>
-      <c r="AA18" s="54" t="s">
+      <c r="AA18" s="49" t="s">
         <v>242</v>
       </c>
       <c r="AB18" s="9" t="s">
@@ -5917,7 +5913,7 @@
       <c r="L19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M19" s="56" t="s">
+      <c r="M19" s="51" t="s">
         <v>247</v>
       </c>
       <c r="N19" s="9" t="s">
@@ -5941,7 +5937,7 @@
       <c r="U19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W19" s="53">
+      <c r="W19" s="48">
         <v>92</v>
       </c>
       <c r="X19" s="1" t="s">
@@ -5951,7 +5947,7 @@
         <v>7</v>
       </c>
       <c r="Z19" s="1"/>
-      <c r="AA19" s="54" t="s">
+      <c r="AA19" s="49" t="s">
         <v>249</v>
       </c>
       <c r="AB19" s="9" t="s">
@@ -5983,13 +5979,13 @@
       <c r="L20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="56" t="s">
+      <c r="M20" s="51" t="s">
         <v>252</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P20" s="53">
+      <c r="P20" s="48">
         <v>93</v>
       </c>
       <c r="Q20" s="1" t="s">
@@ -6001,13 +5997,13 @@
       <c r="S20" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T20" s="54" t="s">
+      <c r="T20" s="49" t="s">
         <v>254</v>
       </c>
       <c r="U20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W20" s="53">
+      <c r="W20" s="48">
         <v>94</v>
       </c>
       <c r="X20" s="1" t="s">
@@ -6017,7 +6013,7 @@
         <v>7</v>
       </c>
       <c r="Z20" s="1"/>
-      <c r="AA20" s="54" t="s">
+      <c r="AA20" s="49" t="s">
         <v>256</v>
       </c>
       <c r="AB20" s="9" t="s">
@@ -6053,13 +6049,13 @@
       <c r="L21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="56" t="s">
+      <c r="M21" s="51" t="s">
         <v>258</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P21" s="53">
+      <c r="P21" s="48">
         <v>95</v>
       </c>
       <c r="Q21" s="1" t="s">
@@ -6071,13 +6067,13 @@
       <c r="S21" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T21" s="54" t="s">
+      <c r="T21" s="49" t="s">
         <v>260</v>
       </c>
       <c r="U21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W21" s="53">
+      <c r="W21" s="48">
         <v>96</v>
       </c>
       <c r="X21" s="1" t="s">
@@ -6087,7 +6083,7 @@
         <v>7</v>
       </c>
       <c r="Z21" s="1"/>
-      <c r="AA21" s="54" t="s">
+      <c r="AA21" s="49" t="s">
         <v>262</v>
       </c>
       <c r="AB21" s="9" t="s">
@@ -6121,7 +6117,7 @@
       </c>
       <c r="M22" s="6"/>
       <c r="N22" s="7"/>
-      <c r="P22" s="53">
+      <c r="P22" s="48">
         <v>97</v>
       </c>
       <c r="Q22" s="1" t="s">
@@ -6133,13 +6129,13 @@
       <c r="S22" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T22" s="54" t="s">
+      <c r="T22" s="49" t="s">
         <v>266</v>
       </c>
       <c r="U22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W22" s="53">
+      <c r="W22" s="48">
         <v>98</v>
       </c>
       <c r="X22" s="1" t="s">
@@ -6149,7 +6145,7 @@
         <v>7</v>
       </c>
       <c r="Z22" s="1"/>
-      <c r="AA22" s="54" t="s">
+      <c r="AA22" s="49" t="s">
         <v>268</v>
       </c>
       <c r="AB22" s="9" t="s">
@@ -6183,7 +6179,7 @@
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="7"/>
-      <c r="P23" s="53">
+      <c r="P23" s="48">
         <v>99</v>
       </c>
       <c r="Q23" s="1" t="s">
@@ -6195,13 +6191,13 @@
       <c r="S23" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T23" s="54" t="s">
+      <c r="T23" s="49" t="s">
         <v>271</v>
       </c>
       <c r="U23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W23" s="53">
+      <c r="W23" s="48">
         <v>100</v>
       </c>
       <c r="X23" s="1" t="s">
@@ -6211,7 +6207,7 @@
         <v>7</v>
       </c>
       <c r="Z23" s="1"/>
-      <c r="AA23" s="54" t="s">
+      <c r="AA23" s="49" t="s">
         <v>273</v>
       </c>
       <c r="AB23" s="9" t="s">
@@ -6249,7 +6245,7 @@
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="7"/>
-      <c r="P24" s="53">
+      <c r="P24" s="48">
         <v>101</v>
       </c>
       <c r="Q24" s="1" t="s">
@@ -6259,13 +6255,13 @@
         <v>7</v>
       </c>
       <c r="S24" s="1"/>
-      <c r="T24" s="54" t="s">
+      <c r="T24" s="49" t="s">
         <v>276</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W24" s="53">
+      <c r="W24" s="48">
         <v>102</v>
       </c>
       <c r="X24" s="1" t="s">
@@ -6275,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="Z24" s="1"/>
-      <c r="AA24" s="54" t="s">
+      <c r="AA24" s="49" t="s">
         <v>278</v>
       </c>
       <c r="AB24" s="9" t="s">
@@ -6309,7 +6305,7 @@
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="7"/>
-      <c r="P25" s="53">
+      <c r="P25" s="48">
         <v>103</v>
       </c>
       <c r="Q25" s="1" t="s">
@@ -6319,13 +6315,13 @@
         <v>7</v>
       </c>
       <c r="S25" s="1"/>
-      <c r="T25" s="54" t="s">
+      <c r="T25" s="49" t="s">
         <v>281</v>
       </c>
       <c r="U25" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W25" s="53">
+      <c r="W25" s="48">
         <v>104</v>
       </c>
       <c r="X25" s="1" t="s">
@@ -6335,7 +6331,7 @@
         <v>7</v>
       </c>
       <c r="Z25" s="1"/>
-      <c r="AA25" s="54" t="s">
+      <c r="AA25" s="49" t="s">
         <v>283</v>
       </c>
       <c r="AB25" s="9" t="s">
@@ -6385,7 +6381,7 @@
       <c r="U26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W26" s="53">
+      <c r="W26" s="48">
         <v>106</v>
       </c>
       <c r="X26" s="1" t="s">
@@ -6395,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="Z26" s="1"/>
-      <c r="AA26" s="54" t="s">
+      <c r="AA26" s="49" t="s">
         <v>287</v>
       </c>
       <c r="AB26" s="9" t="s">
@@ -6433,7 +6429,7 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="7"/>
-      <c r="P27" s="53">
+      <c r="P27" s="48">
         <v>107</v>
       </c>
       <c r="Q27" s="1" t="s">
@@ -6443,13 +6439,13 @@
         <v>6</v>
       </c>
       <c r="S27" s="1"/>
-      <c r="T27" s="54" t="s">
+      <c r="T27" s="49" t="s">
         <v>289</v>
       </c>
       <c r="U27" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="W27" s="53">
+      <c r="W27" s="48">
         <v>108</v>
       </c>
       <c r="X27" s="1" t="s">
@@ -6459,7 +6455,7 @@
         <v>7</v>
       </c>
       <c r="Z27" s="1"/>
-      <c r="AA27" s="54" t="s">
+      <c r="AA27" s="49" t="s">
         <v>291</v>
       </c>
       <c r="AB27" s="9" t="s">
@@ -6493,7 +6489,7 @@
       </c>
       <c r="M28" s="6"/>
       <c r="N28" s="7"/>
-      <c r="P28" s="53">
+      <c r="P28" s="48">
         <v>109</v>
       </c>
       <c r="Q28" s="1" t="s">
@@ -6503,7 +6499,7 @@
         <v>6</v>
       </c>
       <c r="S28" s="1"/>
-      <c r="T28" s="54" t="s">
+      <c r="T28" s="49" t="s">
         <v>294</v>
       </c>
       <c r="U28" s="9" t="s">
@@ -6553,7 +6549,7 @@
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="7"/>
-      <c r="P29" s="53">
+      <c r="P29" s="48">
         <v>111</v>
       </c>
       <c r="Q29" s="1" t="s">
@@ -6565,13 +6561,13 @@
       <c r="S29" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T29" s="55" t="s">
+      <c r="T29" s="50" t="s">
         <v>298</v>
       </c>
       <c r="U29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W29" s="53">
+      <c r="W29" s="48">
         <v>112</v>
       </c>
       <c r="X29" s="1" t="s">
@@ -6621,7 +6617,7 @@
       </c>
       <c r="M30" s="6"/>
       <c r="N30" s="7"/>
-      <c r="P30" s="53">
+      <c r="P30" s="48">
         <v>113</v>
       </c>
       <c r="Q30" s="1" t="s">
@@ -6633,13 +6629,13 @@
       <c r="S30" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T30" s="55" t="s">
+      <c r="T30" s="50" t="s">
         <v>302</v>
       </c>
       <c r="U30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W30" s="53">
+      <c r="W30" s="48">
         <v>114</v>
       </c>
       <c r="X30" s="1" t="s">
@@ -6685,7 +6681,7 @@
       </c>
       <c r="M31" s="6"/>
       <c r="N31" s="7"/>
-      <c r="P31" s="53">
+      <c r="P31" s="48">
         <v>115</v>
       </c>
       <c r="Q31" s="1" t="s">
@@ -6697,13 +6693,13 @@
       <c r="S31" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="T31" s="55" t="s">
+      <c r="T31" s="50" t="s">
         <v>307</v>
       </c>
       <c r="U31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W31" s="53">
+      <c r="W31" s="48">
         <v>116</v>
       </c>
       <c r="X31" s="1" t="s">
@@ -6747,7 +6743,7 @@
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="7"/>
-      <c r="P32" s="53">
+      <c r="P32" s="48">
         <v>117</v>
       </c>
       <c r="Q32" s="1" t="s">
@@ -6757,13 +6753,13 @@
         <v>6</v>
       </c>
       <c r="S32" s="1"/>
-      <c r="T32" s="55" t="s">
+      <c r="T32" s="50" t="s">
         <v>312</v>
       </c>
       <c r="U32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W32" s="53">
+      <c r="W32" s="48">
         <v>118</v>
       </c>
       <c r="X32" s="1" t="s">
@@ -6875,18 +6871,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-    </row>
-    <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="P2" s="39"/>
-    </row>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+    </row>
+    <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>0</v>
@@ -6924,7 +6918,6 @@
       <c r="N3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="39"/>
     </row>
     <row r="4" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="8">
@@ -6940,7 +6933,7 @@
       <c r="F4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I4" s="5">
@@ -6961,7 +6954,6 @@
       <c r="N4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="39"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B5" s="8">
@@ -6977,7 +6969,7 @@
       <c r="F5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I5" s="5">
@@ -6998,7 +6990,6 @@
       <c r="N5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="39"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B6" s="8">
@@ -7014,7 +7005,7 @@
       <c r="F6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I6" s="8">
@@ -7030,10 +7021,9 @@
       <c r="M6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="N6" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P6" s="39"/>
+      <c r="N6" s="41" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B7" s="8">
@@ -7049,7 +7039,7 @@
       <c r="F7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I7" s="8">
@@ -7067,10 +7057,10 @@
       <c r="M7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="40"/>
+      <c r="N7" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="38"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="8">
@@ -7086,7 +7076,7 @@
       <c r="F8" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I8" s="8">
@@ -7102,10 +7092,9 @@
       <c r="M8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P8" s="41"/>
+      <c r="N8" s="41" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B9" s="8">
@@ -7123,7 +7112,7 @@
       <c r="F9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I9" s="8">
@@ -7139,10 +7128,9 @@
       <c r="M9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N9" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="41"/>
+      <c r="N9" s="41" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="8">
@@ -7160,7 +7148,7 @@
       <c r="F10" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I10" s="8">
@@ -7176,10 +7164,10 @@
       <c r="M10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N10" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P10" s="42"/>
+      <c r="N10" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" s="53"/>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="8">
@@ -7195,7 +7183,7 @@
       <c r="F11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I11" s="8">
@@ -7211,10 +7199,10 @@
       <c r="M11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P11" s="42"/>
+      <c r="N11" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="53"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="8">
@@ -7230,7 +7218,7 @@
       <c r="F12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I12" s="8">
@@ -7246,10 +7234,10 @@
       <c r="M12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="N12" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P12" s="43"/>
+      <c r="N12" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="40"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -7279,10 +7267,10 @@
       <c r="M13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N13" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="44"/>
+      <c r="N13" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="39"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B14" s="8">
@@ -7312,10 +7300,10 @@
       <c r="M14" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N14" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P14" s="44"/>
+      <c r="N14" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="39"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="8">
@@ -7331,7 +7319,7 @@
       <c r="F15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="43" t="s">
         <v>243</v>
       </c>
       <c r="I15" s="8">
@@ -7347,10 +7335,10 @@
       <c r="M15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="N15" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P15" s="44"/>
+      <c r="N15" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="39"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B16" s="8">
@@ -7366,7 +7354,7 @@
       <c r="F16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I16" s="8">
@@ -7382,12 +7370,12 @@
       <c r="M16" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="N16" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P16" s="45"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="N16" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P16" s="38"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B17" s="8">
         <v>14</v>
       </c>
@@ -7401,7 +7389,7 @@
       <c r="F17" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="46" t="s">
+      <c r="G17" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I17" s="8">
@@ -7419,12 +7407,11 @@
       <c r="M17" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N17" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="P17" s="41"/>
-    </row>
-    <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N17" s="44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="8">
         <v>15</v>
       </c>
@@ -7440,7 +7427,7 @@
       <c r="F18" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I18" s="5">
@@ -7461,9 +7448,8 @@
       <c r="N18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="41"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B19" s="8">
         <v>16</v>
       </c>
@@ -7496,9 +7482,8 @@
       <c r="N19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="P19" s="41"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
         <v>17</v>
       </c>
@@ -7526,12 +7511,11 @@
       <c r="M20" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="N20" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="P20" s="41"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="N20" s="44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
         <v>18</v>
       </c>
@@ -7547,7 +7531,7 @@
       <c r="F21" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I21" s="8">
@@ -7563,12 +7547,11 @@
       <c r="M21" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="N21" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="P21" s="41"/>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="N21" s="44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B22" s="5">
         <v>19</v>
       </c>
@@ -7600,12 +7583,11 @@
       <c r="M22" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="N22" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P22" s="41"/>
-    </row>
-    <row r="23" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="N22" s="41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="10">
         <v>20</v>
       </c>
@@ -7637,21 +7619,15 @@
       <c r="M23" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="N23" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="P23" s="39"/>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="P24" s="39"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="N23" s="42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.15">
       <c r="E25" s="22"/>
-      <c r="P25" s="39"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.15">
       <c r="C26" s="23"/>
-      <c r="P26" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7688,13 +7664,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
       <c r="G1" s="17"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>

--- a/doc/FPGA_MSXtR_Stack_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_Stack_TangFPGA_pin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA6E0B5-E928-455D-A937-CD0462AD9BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B20DF5-19D9-41ED-9307-49340BE8DEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="349">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1283,14 +1283,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>dipsw2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>dipsw3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>slot_rfsh_n</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1329,10 +1321,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>mcu_csclk</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mcu_mosi</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1365,15 +1353,55 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>slot_a19</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>slot_oe_n</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>slot_data_dir</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom_sclk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mcu_sclk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom_cs_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom_mosi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom_miso</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_rom0_ce_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_rom1_ce_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_cs1_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_cs2_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_cs12_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slot_clock_n</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1415,7 +1443,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1509,6 +1537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1697,7 +1731,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1852,6 +1886,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2932,7 +2969,7 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="49" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>7</v>
@@ -2948,7 +2985,7 @@
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="49" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>7</v>
@@ -2982,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="AA6" s="49" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AB6" s="9" t="s">
         <v>7</v>
@@ -3017,8 +3054,12 @@
         <v>2</v>
       </c>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="9"/>
+      <c r="M7" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="P7" s="48">
         <v>67</v>
       </c>
@@ -3085,8 +3126,12 @@
         <v>2</v>
       </c>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="9"/>
+      <c r="M8" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="P8" s="48">
         <v>69</v>
       </c>
@@ -3151,8 +3196,12 @@
         <v>2</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="9"/>
+      <c r="M9" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="P9" s="48">
         <v>71</v>
       </c>
@@ -3214,7 +3263,7 @@
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>6</v>
@@ -3284,7 +3333,7 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="13" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>6</v>
@@ -3352,7 +3401,7 @@
         <v>198</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>6</v>
@@ -3369,8 +3418,12 @@
       <c r="S12" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T12" s="1"/>
-      <c r="U12" s="9"/>
+      <c r="T12" s="49" t="s">
+        <v>348</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="W12" s="48">
         <v>78</v>
       </c>
@@ -3416,7 +3469,7 @@
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="13" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>7</v>
@@ -3488,7 +3541,7 @@
         <v>5</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>7</v>
@@ -3560,7 +3613,7 @@
         <v>8</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>7</v>
@@ -3576,7 +3629,7 @@
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="U15" s="9" t="s">
         <v>7</v>
@@ -3632,7 +3685,7 @@
         <v>5</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>7</v>
@@ -3649,8 +3702,12 @@
       <c r="S16" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="T16" s="1"/>
-      <c r="U16" s="9"/>
+      <c r="T16" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="W16" s="5">
         <v>86</v>
       </c>
@@ -3702,7 +3759,7 @@
         <v>8</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>7</v>
@@ -3770,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="51" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>7</v>
@@ -3836,7 +3893,7 @@
         <v>8</v>
       </c>
       <c r="M19" s="51" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>7</v>
@@ -3902,7 +3959,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>7</v>
@@ -3972,7 +4029,7 @@
         <v>8</v>
       </c>
       <c r="M21" s="51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>7</v>
@@ -4052,7 +4109,7 @@
         <v>165</v>
       </c>
       <c r="T22" s="49" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="U22" s="9" t="s">
         <v>6</v>
@@ -4114,7 +4171,7 @@
         <v>165</v>
       </c>
       <c r="T23" s="49" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="U23" s="9" t="s">
         <v>6</v>
@@ -4178,7 +4235,7 @@
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="49" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>7</v>
@@ -4484,7 +4541,7 @@
         <v>165</v>
       </c>
       <c r="T29" s="49" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="U29" s="9" t="s">
         <v>7</v>
@@ -4501,11 +4558,11 @@
       <c r="Z29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="49" t="s">
-        <v>202</v>
+      <c r="AA29" s="52" t="s">
+        <v>338</v>
       </c>
       <c r="AB29" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.15">
@@ -4552,7 +4609,7 @@
         <v>165</v>
       </c>
       <c r="T30" s="49" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="U30" s="9" t="s">
         <v>7</v>
@@ -4569,11 +4626,11 @@
       <c r="Z30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA30" s="49" t="s">
-        <v>226</v>
+      <c r="AA30" s="52" t="s">
+        <v>340</v>
       </c>
       <c r="AB30" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.15">
@@ -4616,7 +4673,7 @@
         <v>198</v>
       </c>
       <c r="T31" s="49" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="U31" s="9" t="s">
         <v>7</v>
@@ -4631,11 +4688,11 @@
         <v>6</v>
       </c>
       <c r="Z31" s="1"/>
-      <c r="AA31" s="49" t="s">
-        <v>317</v>
+      <c r="AA31" s="52" t="s">
+        <v>341</v>
       </c>
       <c r="AB31" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.15">
@@ -4676,7 +4733,7 @@
       </c>
       <c r="S32" s="1"/>
       <c r="T32" s="49" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="U32" s="9" t="s">
         <v>7</v>
@@ -4691,8 +4748,8 @@
         <v>6</v>
       </c>
       <c r="Z32" s="1"/>
-      <c r="AA32" s="49" t="s">
-        <v>318</v>
+      <c r="AA32" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="AB32" s="9" t="s">
         <v>6</v>
@@ -6871,14 +6928,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -7167,7 +7224,7 @@
       <c r="N10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="53"/>
+      <c r="P10" s="54"/>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="8">
@@ -7202,7 +7259,7 @@
       <c r="N11" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P11" s="53"/>
+      <c r="P11" s="54"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="8">
@@ -7664,13 +7721,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
       <c r="G1" s="17"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
